--- a/ejes/Políticas/Reporte Política Pública Distrital de Juventud.xlsx
+++ b/ejes/Políticas/Reporte Política Pública Distrital de Juventud.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1401,6 +1401,38 @@
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Política Pública</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Política Pública Distrital de Juventud</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.1.7 Jóvenes que participan en la oferta del Sistema Distrital del Cuidado</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SIDICU</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>María Angélica y Jorge (equipo de Gestión y Análisis de Datos)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N14">
     <filterColumn colId="4" hiddenButton="0" showButton="1">

--- a/ejes/Políticas/Reporte Política Pública Distrital de Juventud.xlsx
+++ b/ejes/Políticas/Reporte Política Pública Distrital de Juventud.xlsx
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.1.7 Jóvenes que participan en la oferta del Sistema Distrital del Cuidado</t>
+          <t>1.1.8 Número de jóvenes atendidos en los servicios del Sistema Distrital de Cuidado</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1430,6 +1430,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>María Angélica y Jorge (equipo de Gestión y Análisis de Datos)</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Producto que empezó su implementación en el segundo trimestre del 2025.</t>
         </is>
       </c>
     </row>
